--- a/assignment3/Code-Clone-Detection-Techniques/results.xlsx
+++ b/assignment3/Code-Clone-Detection-Techniques/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kylen\gth842\cmpt470-a2\repo\assignment3\Code-Clone-Detection-Techniques\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05D838B1-F23E-4F73-8ED7-84AFDD2117E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D0FD12-2C27-490B-B945-634CDA8A2C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{84CCF75C-8D01-4337-95EC-777F0C990642}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="4">
   <si>
     <t>NO</t>
   </si>
@@ -71,7 +71,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -79,12 +79,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -419,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F27B32-BCEE-4B2A-9F74-6616CE796D5C}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -577,11 +588,251 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/assignment3/Code-Clone-Detection-Techniques/results.xlsx
+++ b/assignment3/Code-Clone-Detection-Techniques/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kylen\gth842\cmpt470-a2\repo\assignment3\Code-Clone-Detection-Techniques\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D0FD12-2C27-490B-B945-634CDA8A2C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD982D0-FDD7-413C-A67A-CCC3A7F5E5D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{84CCF75C-8D01-4337-95EC-777F0C990642}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="5">
   <si>
     <t>NO</t>
   </si>
@@ -47,15 +47,26 @@
     <t xml:space="preserve"> NO</t>
   </si>
   <si>
-    <t>x</t>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>Result</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -71,7 +82,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -80,9 +91,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right/>
-      <top/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -92,10 +120,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,411 +459,466 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F27B32-BCEE-4B2A-9F74-6616CE796D5C}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>0</v>
-      </c>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" t="s">
-        <v>3</v>
-      </c>
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" t="s">
-        <v>0</v>
-      </c>
+      <c r="A18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="C20" s="1"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>0</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>0</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>0</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>0</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>0</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>0</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="1"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="1"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="1"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="1"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="1"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="1"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="1"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C46" s="1"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="1"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="1"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C49" s="1"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C50" s="1"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C51" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
